--- a/docs/cc_booking_2025.xlsx
+++ b/docs/cc_booking_2025.xlsx
@@ -34006,78 +34006,78 @@
     </row>
   </sheetData>
   <mergeCells count="72">
-    <mergeCell ref="A292:C292"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:H1"/>
     <mergeCell ref="I1:L1"/>
+    <mergeCell ref="M1"/>
+    <mergeCell ref="N1:Q1"/>
+    <mergeCell ref="R1:U1"/>
+    <mergeCell ref="A34:C34"/>
     <mergeCell ref="D34:H34"/>
-    <mergeCell ref="I64:L64"/>
-    <mergeCell ref="R97:U97"/>
-    <mergeCell ref="N162:Q162"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="M97"/>
-    <mergeCell ref="R357:U357"/>
-    <mergeCell ref="N34:Q34"/>
-    <mergeCell ref="M194"/>
-    <mergeCell ref="N260:Q260"/>
-    <mergeCell ref="A129:C129"/>
-    <mergeCell ref="R260:U260"/>
-    <mergeCell ref="M357"/>
-    <mergeCell ref="N325:Q325"/>
-    <mergeCell ref="R1:U1"/>
-    <mergeCell ref="M162"/>
-    <mergeCell ref="A194:C194"/>
     <mergeCell ref="I34:L34"/>
     <mergeCell ref="M34"/>
+    <mergeCell ref="N34:Q34"/>
+    <mergeCell ref="R34:U34"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="D64:H64"/>
+    <mergeCell ref="I64:L64"/>
+    <mergeCell ref="M64"/>
+    <mergeCell ref="N64:Q64"/>
+    <mergeCell ref="R64:U64"/>
     <mergeCell ref="A97:C97"/>
-    <mergeCell ref="R64:U64"/>
+    <mergeCell ref="D97:H97"/>
+    <mergeCell ref="I97:L97"/>
+    <mergeCell ref="M97"/>
+    <mergeCell ref="N97:Q97"/>
+    <mergeCell ref="R97:U97"/>
+    <mergeCell ref="A129:C129"/>
+    <mergeCell ref="D129:H129"/>
+    <mergeCell ref="I129:L129"/>
+    <mergeCell ref="M129"/>
     <mergeCell ref="N129:Q129"/>
+    <mergeCell ref="R129:U129"/>
+    <mergeCell ref="A162:C162"/>
+    <mergeCell ref="D162:H162"/>
+    <mergeCell ref="I162:L162"/>
+    <mergeCell ref="M162"/>
+    <mergeCell ref="N162:Q162"/>
+    <mergeCell ref="R162:U162"/>
+    <mergeCell ref="A194:C194"/>
+    <mergeCell ref="D194:H194"/>
+    <mergeCell ref="I194:L194"/>
+    <mergeCell ref="M194"/>
+    <mergeCell ref="N194:Q194"/>
+    <mergeCell ref="R194:U194"/>
+    <mergeCell ref="A227:C227"/>
+    <mergeCell ref="D227:H227"/>
+    <mergeCell ref="I227:L227"/>
+    <mergeCell ref="M227"/>
     <mergeCell ref="N227:Q227"/>
-    <mergeCell ref="D194:H194"/>
+    <mergeCell ref="R227:U227"/>
+    <mergeCell ref="A260:C260"/>
+    <mergeCell ref="D260:H260"/>
     <mergeCell ref="I260:L260"/>
+    <mergeCell ref="M260"/>
+    <mergeCell ref="N260:Q260"/>
+    <mergeCell ref="R260:U260"/>
+    <mergeCell ref="A292:C292"/>
+    <mergeCell ref="D292:H292"/>
+    <mergeCell ref="I292:L292"/>
+    <mergeCell ref="M292"/>
+    <mergeCell ref="N292:Q292"/>
+    <mergeCell ref="R292:U292"/>
+    <mergeCell ref="A325:C325"/>
     <mergeCell ref="D325:H325"/>
-    <mergeCell ref="D97:H97"/>
-    <mergeCell ref="N292:Q292"/>
-    <mergeCell ref="M260"/>
-    <mergeCell ref="M129"/>
     <mergeCell ref="I325:L325"/>
+    <mergeCell ref="M325"/>
+    <mergeCell ref="N325:Q325"/>
+    <mergeCell ref="R325:U325"/>
     <mergeCell ref="A357:C357"/>
-    <mergeCell ref="D162:H162"/>
-    <mergeCell ref="M1"/>
-    <mergeCell ref="N97:Q97"/>
-    <mergeCell ref="M64"/>
-    <mergeCell ref="R162:U162"/>
-    <mergeCell ref="D227:H227"/>
+    <mergeCell ref="D357:H357"/>
+    <mergeCell ref="I357:L357"/>
+    <mergeCell ref="M357"/>
     <mergeCell ref="N357:Q357"/>
-    <mergeCell ref="D292:H292"/>
-    <mergeCell ref="I129:L129"/>
-    <mergeCell ref="R34:U34"/>
-    <mergeCell ref="I194:L194"/>
-    <mergeCell ref="I227:L227"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="D357:H357"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="I292:L292"/>
-    <mergeCell ref="I97:L97"/>
-    <mergeCell ref="A260:C260"/>
-    <mergeCell ref="R227:U227"/>
-    <mergeCell ref="N194:Q194"/>
-    <mergeCell ref="I357:L357"/>
-    <mergeCell ref="R325:U325"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="M227"/>
-    <mergeCell ref="I162:L162"/>
-    <mergeCell ref="A325:C325"/>
-    <mergeCell ref="D64:H64"/>
-    <mergeCell ref="N1:Q1"/>
-    <mergeCell ref="N64:Q64"/>
-    <mergeCell ref="D260:H260"/>
-    <mergeCell ref="M292"/>
-    <mergeCell ref="A162:C162"/>
-    <mergeCell ref="D129:H129"/>
-    <mergeCell ref="R129:U129"/>
-    <mergeCell ref="A227:C227"/>
-    <mergeCell ref="R194:U194"/>
-    <mergeCell ref="M325"/>
-    <mergeCell ref="R292:U292"/>
+    <mergeCell ref="R357:U357"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
